--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/129.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/129.xlsx
@@ -426,13 +426,13 @@
         <v>-16.2350571747275</v>
       </c>
       <c r="E2">
-        <v>-5.419082010518474</v>
+        <v>-4.257297475376635</v>
       </c>
       <c r="F2">
-        <v>-1.591157104947962</v>
+        <v>-1.571167568883285</v>
       </c>
       <c r="G2">
-        <v>-10.15714882007151</v>
+        <v>-9.451065735819132</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.26191692947956</v>
       </c>
       <c r="E3">
-        <v>-5.063746240558603</v>
+        <v>-4.54145921935795</v>
       </c>
       <c r="F3">
-        <v>-1.020872523327794</v>
+        <v>-1.469428717169539</v>
       </c>
       <c r="G3">
-        <v>-9.808799976247238</v>
+        <v>-8.691550446562919</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.32447348427405</v>
       </c>
       <c r="E4">
-        <v>-6.182596313633718</v>
+        <v>-5.229049127260595</v>
       </c>
       <c r="F4">
-        <v>-1.072860837413925</v>
+        <v>-1.33052028762043</v>
       </c>
       <c r="G4">
-        <v>-9.235605500486745</v>
+        <v>-8.665145535341692</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.36656975107342</v>
       </c>
       <c r="E5">
-        <v>-7.333648365377377</v>
+        <v>-5.949823692691447</v>
       </c>
       <c r="F5">
-        <v>-1.125016232474134</v>
+        <v>-1.268524535854638</v>
       </c>
       <c r="G5">
-        <v>-9.219079257154704</v>
+        <v>-7.815924393607847</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.32147987876626</v>
       </c>
       <c r="E6">
-        <v>-8.382909378376622</v>
+        <v>-7.92589578152253</v>
       </c>
       <c r="F6">
-        <v>-0.9433200283546396</v>
+        <v>-0.6947090818959973</v>
       </c>
       <c r="G6">
-        <v>-9.372407173806049</v>
+        <v>-7.553348474160553</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.13427536026503</v>
       </c>
       <c r="E7">
-        <v>-9.162517878115128</v>
+        <v>-7.848273208557052</v>
       </c>
       <c r="F7">
-        <v>-0.68794349022524</v>
+        <v>-0.8693348309560126</v>
       </c>
       <c r="G7">
-        <v>-8.823045315382771</v>
+        <v>-8.227461620140188</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.76959688974614</v>
       </c>
       <c r="E8">
-        <v>-9.877749591360592</v>
+        <v>-9.662859914274611</v>
       </c>
       <c r="F8">
-        <v>-0.5552590249238077</v>
+        <v>-0.6939211882030663</v>
       </c>
       <c r="G8">
-        <v>-8.994048234668284</v>
+        <v>-7.747747018772096</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.20933276954522</v>
       </c>
       <c r="E9">
-        <v>-10.20129094531261</v>
+        <v>-9.177679209092808</v>
       </c>
       <c r="F9">
-        <v>-0.7005624589594616</v>
+        <v>-0.6592206078898725</v>
       </c>
       <c r="G9">
-        <v>-7.838638046552787</v>
+        <v>-6.461994031684413</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.46837033857501</v>
       </c>
       <c r="E10">
-        <v>-11.58275628304054</v>
+        <v>-11.14804089220022</v>
       </c>
       <c r="F10">
-        <v>-0.2324237414733072</v>
+        <v>-1.02249898930295</v>
       </c>
       <c r="G10">
-        <v>-7.607787085008328</v>
+        <v>-5.943347414774493</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.5939827742205</v>
       </c>
       <c r="E11">
-        <v>-12.2757848882264</v>
+        <v>-11.59149170940134</v>
       </c>
       <c r="F11">
-        <v>-0.1670428183132628</v>
+        <v>-0.3826675461121745</v>
       </c>
       <c r="G11">
-        <v>-6.979081381645337</v>
+        <v>-6.441356090792596</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.64915049199984</v>
       </c>
       <c r="E12">
-        <v>-12.22062807481297</v>
+        <v>-12.56526758916673</v>
       </c>
       <c r="F12">
-        <v>-0.4349908139994206</v>
+        <v>-0.4573313614955672</v>
       </c>
       <c r="G12">
-        <v>-6.04765277308031</v>
+        <v>-4.889945066360558</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.70352786771006</v>
       </c>
       <c r="E13">
-        <v>-13.15135628066145</v>
+        <v>-11.16635404108724</v>
       </c>
       <c r="F13">
-        <v>-0.1893580265147623</v>
+        <v>-0.4850596765160388</v>
       </c>
       <c r="G13">
-        <v>-5.326155788797087</v>
+        <v>-5.041948764796195</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.84214283191802</v>
       </c>
       <c r="E14">
-        <v>-14.51165553087753</v>
+        <v>-13.43519650298822</v>
       </c>
       <c r="F14">
-        <v>0.257387991465636</v>
+        <v>-0.4481276545679909</v>
       </c>
       <c r="G14">
-        <v>-4.968706255285359</v>
+        <v>-4.47330959969774</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.13002926730745</v>
       </c>
       <c r="E15">
-        <v>-14.71045553981426</v>
+        <v>-15.02736720781905</v>
       </c>
       <c r="F15">
-        <v>0.1037780199035022</v>
+        <v>-0.3058118817418135</v>
       </c>
       <c r="G15">
-        <v>-4.168395113348707</v>
+        <v>-3.406648516399024</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.601323175756438</v>
       </c>
       <c r="E16">
-        <v>-15.82186985856878</v>
+        <v>-14.9619262299342</v>
       </c>
       <c r="F16">
-        <v>0.5556037746076725</v>
+        <v>0.2462474122034772</v>
       </c>
       <c r="G16">
-        <v>-3.98850337929025</v>
+        <v>-2.259256469579642</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.270737651423174</v>
       </c>
       <c r="E17">
-        <v>-15.91336767589376</v>
+        <v>-16.75973946792735</v>
       </c>
       <c r="F17">
-        <v>0.3382567666257205</v>
+        <v>0.1645646122028568</v>
       </c>
       <c r="G17">
-        <v>-3.125622926661372</v>
+        <v>-2.689024870396748</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.119621581925628</v>
       </c>
       <c r="E18">
-        <v>-17.92731139285099</v>
+        <v>-16.98167997904327</v>
       </c>
       <c r="F18">
-        <v>0.8853265950844191</v>
+        <v>0.114361926536384</v>
       </c>
       <c r="G18">
-        <v>-2.252297702856093</v>
+        <v>-1.281039920908095</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.099311394601123</v>
       </c>
       <c r="E19">
-        <v>-18.46960521221753</v>
+        <v>-18.69832484892294</v>
       </c>
       <c r="F19">
-        <v>0.9221699295012025</v>
+        <v>1.04175397947012</v>
       </c>
       <c r="G19">
-        <v>-1.40388764477937</v>
+        <v>-1.169752622059954</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.161432429462305</v>
       </c>
       <c r="E20">
-        <v>-19.59017157694155</v>
+        <v>-18.5864851263555</v>
       </c>
       <c r="F20">
-        <v>1.110103559368655</v>
+        <v>0.9550460805998099</v>
       </c>
       <c r="G20">
-        <v>-1.042770026810129</v>
+        <v>-1.585911370165118</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.262926354926229</v>
       </c>
       <c r="E21">
-        <v>-19.90247778688054</v>
+        <v>-18.21728769745815</v>
       </c>
       <c r="F21">
-        <v>1.357080913175522</v>
+        <v>0.8830983208613958</v>
       </c>
       <c r="G21">
-        <v>-1.544685146564573</v>
+        <v>-1.39257551067168</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.362478083828666</v>
       </c>
       <c r="E22">
-        <v>-20.50141375913502</v>
+        <v>-20.92644274407294</v>
       </c>
       <c r="F22">
-        <v>1.789120638025149</v>
+        <v>1.257429385858325</v>
       </c>
       <c r="G22">
-        <v>-1.191896861172139</v>
+        <v>0.6424135217727792</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.432150801777489</v>
       </c>
       <c r="E23">
-        <v>-21.03348681266625</v>
+        <v>-21.77322662724123</v>
       </c>
       <c r="F23">
-        <v>1.855431988410514</v>
+        <v>1.516865754101954</v>
       </c>
       <c r="G23">
-        <v>-0.586321939492036</v>
+        <v>0.06005214541404542</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.464717767198197</v>
       </c>
       <c r="E24">
-        <v>-21.99761251432129</v>
+        <v>-20.95527100960577</v>
       </c>
       <c r="F24">
-        <v>1.421390459283771</v>
+        <v>1.638765182119244</v>
       </c>
       <c r="G24">
-        <v>-0.5540507415752205</v>
+        <v>-0.9497768026120018</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.459185962901724</v>
       </c>
       <c r="E25">
-        <v>-21.62299903051077</v>
+        <v>-22.14549436151577</v>
       </c>
       <c r="F25">
-        <v>1.83543136640443</v>
+        <v>1.348394286229336</v>
       </c>
       <c r="G25">
-        <v>-0.6836585994376875</v>
+        <v>-0.7819884230451203</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.421122092432222</v>
       </c>
       <c r="E26">
-        <v>-21.18605110198466</v>
+        <v>-21.63294355943161</v>
       </c>
       <c r="F26">
-        <v>1.571079174999277</v>
+        <v>1.100435034754897</v>
       </c>
       <c r="G26">
-        <v>-1.219957045163002</v>
+        <v>-0.07621653007343518</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.370380036398084</v>
       </c>
       <c r="E27">
-        <v>-22.32508458371197</v>
+        <v>-21.27072903745409</v>
       </c>
       <c r="F27">
-        <v>1.643077613326985</v>
+        <v>1.157202973293824</v>
       </c>
       <c r="G27">
-        <v>-0.3400835622810451</v>
+        <v>-0.5556828405260812</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.320891025575182</v>
       </c>
       <c r="E28">
-        <v>-21.71731808714253</v>
+        <v>-21.754791209556</v>
       </c>
       <c r="F28">
-        <v>1.711742350702693</v>
+        <v>1.62390368580876</v>
       </c>
       <c r="G28">
-        <v>-0.7533025459473355</v>
+        <v>-1.039045663078449</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.279275719009062</v>
       </c>
       <c r="E29">
-        <v>-22.00080961697071</v>
+        <v>-22.12098173171226</v>
       </c>
       <c r="F29">
-        <v>1.869203895051176</v>
+        <v>1.221463424518695</v>
       </c>
       <c r="G29">
-        <v>-1.084575595880046</v>
+        <v>-0.751442019354265</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.255550018488645</v>
       </c>
       <c r="E30">
-        <v>-22.4602414189449</v>
+        <v>-21.73663655725925</v>
       </c>
       <c r="F30">
-        <v>1.764671386102595</v>
+        <v>1.52319424294005</v>
       </c>
       <c r="G30">
-        <v>-1.420264913562144</v>
+        <v>-0.4981223852347731</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.251949101265136</v>
       </c>
       <c r="E31">
-        <v>-21.58863244126656</v>
+        <v>-21.2221430398258</v>
       </c>
       <c r="F31">
-        <v>1.789252085616131</v>
+        <v>1.930683358688535</v>
       </c>
       <c r="G31">
-        <v>-1.236019812119546</v>
+        <v>-2.167272961770991</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.261957731929462</v>
       </c>
       <c r="E32">
-        <v>-21.51536626029646</v>
+        <v>-20.88017079666256</v>
       </c>
       <c r="F32">
-        <v>1.541913646860544</v>
+        <v>1.388777203367127</v>
       </c>
       <c r="G32">
-        <v>-1.319200579339274</v>
+        <v>-0.7518624586377525</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.283886428571526</v>
       </c>
       <c r="E33">
-        <v>-20.53543165588064</v>
+        <v>-21.81638298453433</v>
       </c>
       <c r="F33">
-        <v>1.813067855172509</v>
+        <v>1.717168127168989</v>
       </c>
       <c r="G33">
-        <v>-1.943446977860867</v>
+        <v>-1.384951324294739</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.315056154154751</v>
       </c>
       <c r="E34">
-        <v>-20.76266595311153</v>
+        <v>-20.81556305799513</v>
       </c>
       <c r="F34">
-        <v>1.938198043257295</v>
+        <v>1.777284020013155</v>
       </c>
       <c r="G34">
-        <v>-1.930578887349719</v>
+        <v>-1.178605020831966</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.347994991350983</v>
       </c>
       <c r="E35">
-        <v>-20.3774830109671</v>
+        <v>-19.28678193232367</v>
       </c>
       <c r="F35">
-        <v>2.199186443298054</v>
+        <v>1.302458896152015</v>
       </c>
       <c r="G35">
-        <v>-2.873889043855191</v>
+        <v>-2.079510399524912</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.377902123340233</v>
       </c>
       <c r="E36">
-        <v>-20.34401758805042</v>
+        <v>-18.86237334832481</v>
       </c>
       <c r="F36">
-        <v>2.402326817365557</v>
+        <v>1.931978830127365</v>
       </c>
       <c r="G36">
-        <v>-1.852926731180574</v>
+        <v>-1.554729341730722</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.403981485734525</v>
       </c>
       <c r="E37">
-        <v>-18.92214920522605</v>
+        <v>-19.17760495247274</v>
       </c>
       <c r="F37">
-        <v>2.44929636740566</v>
+        <v>1.556996861999189</v>
       </c>
       <c r="G37">
-        <v>-2.872564825639482</v>
+        <v>-1.901581818971243</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.420919213331986</v>
       </c>
       <c r="E38">
-        <v>-18.33591560256309</v>
+        <v>-18.6032495371319</v>
       </c>
       <c r="F38">
-        <v>2.297347703348823</v>
+        <v>1.951844837130637</v>
       </c>
       <c r="G38">
-        <v>-3.476272599635437</v>
+        <v>-1.758923790592969</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.422235012271358</v>
       </c>
       <c r="E39">
-        <v>-17.6425156625086</v>
+        <v>-17.44145594504204</v>
       </c>
       <c r="F39">
-        <v>2.431053658965713</v>
+        <v>2.414877686745414</v>
       </c>
       <c r="G39">
-        <v>-3.01720587079578</v>
+        <v>-2.30750436026898</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.413346724730141</v>
       </c>
       <c r="E40">
-        <v>-18.3150257519657</v>
+        <v>-18.32887835395517</v>
       </c>
       <c r="F40">
-        <v>2.967340825699142</v>
+        <v>2.218825980355419</v>
       </c>
       <c r="G40">
-        <v>-2.831997400601253</v>
+        <v>-1.67842787580559</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.397688548267459</v>
       </c>
       <c r="E41">
-        <v>-17.07941350507681</v>
+        <v>-17.26685610120231</v>
       </c>
       <c r="F41">
-        <v>2.731717059600062</v>
+        <v>1.717302742171801</v>
       </c>
       <c r="G41">
-        <v>-3.819946953158257</v>
+        <v>-2.359317708504113</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.377120894792267</v>
       </c>
       <c r="E42">
-        <v>-16.37427576039445</v>
+        <v>-15.16598832566784</v>
       </c>
       <c r="F42">
-        <v>2.626744280406989</v>
+        <v>2.073674582087647</v>
       </c>
       <c r="G42">
-        <v>-3.076567262860451</v>
+        <v>-2.274276414691315</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.365810079064714</v>
       </c>
       <c r="E43">
-        <v>-15.23209951770582</v>
+        <v>-16.10389869129248</v>
       </c>
       <c r="F43">
-        <v>2.455772140893892</v>
+        <v>1.989614639507952</v>
       </c>
       <c r="G43">
-        <v>-3.476613585825981</v>
+        <v>-2.187467289560546</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.375482422873446</v>
       </c>
       <c r="E44">
-        <v>-14.39520582177029</v>
+        <v>-15.32577100255448</v>
       </c>
       <c r="F44">
-        <v>3.021492482065764</v>
+        <v>1.687391288546896</v>
       </c>
       <c r="G44">
-        <v>-3.374609056669958</v>
+        <v>-2.270552050959635</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.4109562249677</v>
       </c>
       <c r="E45">
-        <v>-14.85374551436496</v>
+        <v>-13.56047673641042</v>
       </c>
       <c r="F45">
-        <v>2.754489166958165</v>
+        <v>1.613737877537554</v>
       </c>
       <c r="G45">
-        <v>-3.348535200002658</v>
+        <v>-2.759979792939947</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.483515468741512</v>
       </c>
       <c r="E46">
-        <v>-14.36173134190559</v>
+        <v>-13.48591088340012</v>
       </c>
       <c r="F46">
-        <v>2.837334407100718</v>
+        <v>1.897737524529648</v>
       </c>
       <c r="G46">
-        <v>-3.148469001427882</v>
+        <v>-2.899767578335673</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.601763126350107</v>
       </c>
       <c r="E47">
-        <v>-13.44468365603429</v>
+        <v>-13.3671154247569</v>
       </c>
       <c r="F47">
-        <v>2.609106547626739</v>
+        <v>2.008600106022241</v>
       </c>
       <c r="G47">
-        <v>-3.595309885591011</v>
+        <v>-2.94925030251116</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.765039790465668</v>
       </c>
       <c r="E48">
-        <v>-12.06626145283951</v>
+        <v>-12.70535593259401</v>
       </c>
       <c r="F48">
-        <v>2.583464765149859</v>
+        <v>2.230640426484598</v>
       </c>
       <c r="G48">
-        <v>-2.745012816556903</v>
+        <v>-1.224459387096411</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.972098200287938</v>
       </c>
       <c r="E49">
-        <v>-11.97598179502259</v>
+        <v>-12.62036553241805</v>
       </c>
       <c r="F49">
-        <v>2.507157063026241</v>
+        <v>1.938727001033052</v>
       </c>
       <c r="G49">
-        <v>-2.514804100847063</v>
+        <v>-2.230318991020872</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.22456056678814</v>
       </c>
       <c r="E50">
-        <v>-11.68621380021978</v>
+        <v>-11.96353754844951</v>
       </c>
       <c r="F50">
-        <v>2.676528075858827</v>
+        <v>1.840396284449332</v>
       </c>
       <c r="G50">
-        <v>-2.962363373392213</v>
+        <v>-2.446481062007584</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.51460437110911</v>
       </c>
       <c r="E51">
-        <v>-10.23205286924671</v>
+        <v>-12.13288436244035</v>
       </c>
       <c r="F51">
-        <v>2.691950204063377</v>
+        <v>1.950104344329569</v>
       </c>
       <c r="G51">
-        <v>-3.497562717998489</v>
+        <v>-1.803146057906553</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.83188543541036</v>
       </c>
       <c r="E52">
-        <v>-10.22845273241061</v>
+        <v>-11.04634947988397</v>
       </c>
       <c r="F52">
-        <v>2.244749662485248</v>
+        <v>2.010848968422164</v>
       </c>
       <c r="G52">
-        <v>-2.978105017431448</v>
+        <v>-2.545956334371605</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.17829226034034</v>
       </c>
       <c r="E53">
-        <v>-9.85895642422876</v>
+        <v>-11.16395394986317</v>
       </c>
       <c r="F53">
-        <v>2.50196567503543</v>
+        <v>1.822486154251628</v>
       </c>
       <c r="G53">
-        <v>-2.981504947700279</v>
+        <v>-2.297771356383522</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.55119935077358</v>
       </c>
       <c r="E54">
-        <v>-9.56327877084594</v>
+        <v>-9.395883729152406</v>
       </c>
       <c r="F54">
-        <v>2.311399925936517</v>
+        <v>1.451906888568374</v>
       </c>
       <c r="G54">
-        <v>-3.968123660950496</v>
+        <v>-2.112298042545854</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.9444282768805</v>
       </c>
       <c r="E55">
-        <v>-7.865327441669939</v>
+        <v>-8.721978869700941</v>
       </c>
       <c r="F55">
-        <v>2.450382789663652</v>
+        <v>1.81155699972918</v>
       </c>
       <c r="G55">
-        <v>-3.953067299837891</v>
+        <v>-2.201113358273421</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.36814000718494</v>
       </c>
       <c r="E56">
-        <v>-8.338086542648702</v>
+        <v>-8.76975879895587</v>
       </c>
       <c r="F56">
-        <v>2.382430719949891</v>
+        <v>1.613942175600646</v>
       </c>
       <c r="G56">
-        <v>-3.85658807118691</v>
+        <v>-2.426359566219894</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.82798512752316</v>
       </c>
       <c r="E57">
-        <v>-8.682341136711802</v>
+        <v>-8.048273263105814</v>
       </c>
       <c r="F57">
-        <v>2.753863603121566</v>
+        <v>1.748135912639492</v>
       </c>
       <c r="G57">
-        <v>-3.649678974982461</v>
+        <v>-2.851248222912115</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.32152230102078</v>
       </c>
       <c r="E58">
-        <v>-7.846842210770629</v>
+        <v>-7.754017550561402</v>
       </c>
       <c r="F58">
-        <v>2.497689669063743</v>
+        <v>1.917681133122777</v>
       </c>
       <c r="G58">
-        <v>-3.978088403023702</v>
+        <v>-2.357811410283745</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.85529903329427</v>
       </c>
       <c r="E59">
-        <v>-7.512115526019667</v>
+        <v>-7.336904338188893</v>
       </c>
       <c r="F59">
-        <v>2.503774267190862</v>
+        <v>1.595218020562405</v>
       </c>
       <c r="G59">
-        <v>-3.503938828707126</v>
+        <v>-3.052963073165448</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.42911854193565</v>
       </c>
       <c r="E60">
-        <v>-7.565012630903264</v>
+        <v>-6.102682332820359</v>
       </c>
       <c r="F60">
-        <v>2.200778067743071</v>
+        <v>1.402647299774546</v>
       </c>
       <c r="G60">
-        <v>-4.041286717368389</v>
+        <v>-2.856094861581608</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.0287274197682</v>
       </c>
       <c r="E61">
-        <v>-6.514669312616186</v>
+        <v>-6.052072107310636</v>
       </c>
       <c r="F61">
-        <v>2.574746464085365</v>
+        <v>1.929467072545478</v>
       </c>
       <c r="G61">
-        <v>-4.440372982127531</v>
+        <v>-2.11980967037446</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.63756442858435</v>
       </c>
       <c r="E62">
-        <v>-6.690600527814179</v>
+        <v>-7.168114526500996</v>
       </c>
       <c r="F62">
-        <v>2.410828150719636</v>
+        <v>1.563735530669384</v>
       </c>
       <c r="G62">
-        <v>-4.43415246705924</v>
+        <v>-3.309090049902242</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.24059650919405</v>
       </c>
       <c r="E63">
-        <v>-6.40246278365413</v>
+        <v>-5.955719765849434</v>
       </c>
       <c r="F63">
-        <v>2.274143244275804</v>
+        <v>1.195734538216466</v>
       </c>
       <c r="G63">
-        <v>-4.440667620680526</v>
+        <v>-4.007042434310168</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.81170281574827</v>
       </c>
       <c r="E64">
-        <v>-5.489789603674239</v>
+        <v>-5.358903119430542</v>
       </c>
       <c r="F64">
-        <v>2.394672766676238</v>
+        <v>1.356277974276394</v>
       </c>
       <c r="G64">
-        <v>-4.282019657347572</v>
+        <v>-3.250384145854346</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.32264331831967</v>
       </c>
       <c r="E65">
-        <v>-6.164038627150285</v>
+        <v>-5.793772478387126</v>
       </c>
       <c r="F65">
-        <v>2.097081755517843</v>
+        <v>1.660873716698778</v>
       </c>
       <c r="G65">
-        <v>-4.148766888846367</v>
+        <v>-3.773778085067581</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.76048431542706</v>
       </c>
       <c r="E66">
-        <v>-5.166864122187265</v>
+        <v>-4.819054676028143</v>
       </c>
       <c r="F66">
-        <v>2.384999490944734</v>
+        <v>1.297297598573598</v>
       </c>
       <c r="G66">
-        <v>-4.846494156157624</v>
+        <v>-3.238635019735472</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.10940735908672</v>
       </c>
       <c r="E67">
-        <v>-5.881457320597647</v>
+        <v>-5.396086419507523</v>
       </c>
       <c r="F67">
-        <v>2.258862065897728</v>
+        <v>1.313449815205165</v>
       </c>
       <c r="G67">
-        <v>-3.999534117027101</v>
+        <v>-3.093798652392358</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.35144259185405</v>
       </c>
       <c r="E68">
-        <v>-6.226803276896597</v>
+        <v>-5.536509870011374</v>
       </c>
       <c r="F68">
-        <v>2.116266768977476</v>
+        <v>1.040133848318625</v>
       </c>
       <c r="G68">
-        <v>-4.173980003673457</v>
+        <v>-3.311940429611554</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.48888965997393</v>
       </c>
       <c r="E69">
-        <v>-5.750751975314258</v>
+        <v>-5.134603273356621</v>
       </c>
       <c r="F69">
-        <v>1.879395042617029</v>
+        <v>1.278226611939876</v>
       </c>
       <c r="G69">
-        <v>-4.156619502865519</v>
+        <v>-3.723451171779581</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.52496950392694</v>
       </c>
       <c r="E70">
-        <v>-4.956226682194486</v>
+        <v>-5.302102469952333</v>
       </c>
       <c r="F70">
-        <v>1.950782170461377</v>
+        <v>0.9129179195432052</v>
       </c>
       <c r="G70">
-        <v>-4.470161270889893</v>
+        <v>-3.149829635644523</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.46013907248198</v>
       </c>
       <c r="E71">
-        <v>-5.556512139703253</v>
+        <v>-6.714298032296318</v>
       </c>
       <c r="F71">
-        <v>1.689020921933884</v>
+        <v>1.027972570593966</v>
       </c>
       <c r="G71">
-        <v>-3.796140820185358</v>
+        <v>-3.032083462449264</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.30738420582325</v>
       </c>
       <c r="E72">
-        <v>-5.273188163413358</v>
+        <v>-5.179539320934734</v>
       </c>
       <c r="F72">
-        <v>1.587130034452256</v>
+        <v>1.194096986299902</v>
       </c>
       <c r="G72">
-        <v>-4.00140126471125</v>
+        <v>-2.51863109149046</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.0853946075694</v>
       </c>
       <c r="E73">
-        <v>-6.439523814932904</v>
+        <v>-5.977773434266788</v>
       </c>
       <c r="F73">
-        <v>1.664891578606248</v>
+        <v>1.141199625018309</v>
       </c>
       <c r="G73">
-        <v>-3.530148417741536</v>
+        <v>-3.063950773810289</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-17.80677793987136</v>
       </c>
       <c r="E74">
-        <v>-5.567353306477616</v>
+        <v>-4.794967722781345</v>
       </c>
       <c r="F74">
-        <v>1.539625191812734</v>
+        <v>0.8807465175769682</v>
       </c>
       <c r="G74">
-        <v>-3.744685010868466</v>
+        <v>-2.6398235425921</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.48387355364321</v>
       </c>
       <c r="E75">
-        <v>-6.821962501828681</v>
+        <v>-8.2115655073484</v>
       </c>
       <c r="F75">
-        <v>1.634002978431517</v>
+        <v>0.926287564881345</v>
       </c>
       <c r="G75">
-        <v>-3.511510046355439</v>
+        <v>-2.798315910284708</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.14114586684013</v>
       </c>
       <c r="E76">
-        <v>-6.941156466184572</v>
+        <v>-5.792966410013761</v>
       </c>
       <c r="F76">
-        <v>1.102666476389752</v>
+        <v>0.5835260936027854</v>
       </c>
       <c r="G76">
-        <v>-3.717664338176935</v>
+        <v>-3.036999622575082</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-16.79243811527592</v>
       </c>
       <c r="E77">
-        <v>-6.45251600686091</v>
+        <v>-5.835248771823379</v>
       </c>
       <c r="F77">
-        <v>1.292072952758563</v>
+        <v>0.8307378358851368</v>
       </c>
       <c r="G77">
-        <v>-3.576323906923291</v>
+        <v>-2.522256138855962</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.44316475680811</v>
       </c>
       <c r="E78">
-        <v>-7.004595858558027</v>
+        <v>-6.818443877524721</v>
       </c>
       <c r="F78">
-        <v>1.546661597195032</v>
+        <v>0.7936363574041368</v>
       </c>
       <c r="G78">
-        <v>-3.10641845198806</v>
+        <v>-2.288048284134683</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.1117630530771</v>
       </c>
       <c r="E79">
-        <v>-7.819739293834721</v>
+        <v>-8.74785004170676</v>
       </c>
       <c r="F79">
-        <v>1.054824304390241</v>
+        <v>0.3960319421268669</v>
       </c>
       <c r="G79">
-        <v>-3.292994177490305</v>
+        <v>-3.423740863018281</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.80764244771605</v>
       </c>
       <c r="E80">
-        <v>-9.138231672011992</v>
+        <v>-7.208028496404602</v>
       </c>
       <c r="F80">
-        <v>1.399524231709299</v>
+        <v>0.6217203291654385</v>
       </c>
       <c r="G80">
-        <v>-3.010713890993269</v>
+        <v>-2.244286182651057</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.52694571203252</v>
       </c>
       <c r="E81">
-        <v>-9.455369763717163</v>
+        <v>-9.280330657898681</v>
       </c>
       <c r="F81">
-        <v>1.254729167272501</v>
+        <v>0.2752767416334822</v>
       </c>
       <c r="G81">
-        <v>-3.082906957568156</v>
+        <v>-1.269598675524373</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.27637520543219</v>
       </c>
       <c r="E82">
-        <v>-10.06658695748045</v>
+        <v>-10.2992327811505</v>
       </c>
       <c r="F82">
-        <v>1.048931334678891</v>
+        <v>0.187900518866857</v>
       </c>
       <c r="G82">
-        <v>-2.871369718699806</v>
+        <v>-2.069085491621747</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.05756222897002</v>
       </c>
       <c r="E83">
-        <v>-10.60829207522599</v>
+        <v>-10.05046106153913</v>
       </c>
       <c r="F83">
-        <v>0.9373402484651969</v>
+        <v>0.1064758629304533</v>
       </c>
       <c r="G83">
-        <v>-2.384961194251308</v>
+        <v>-2.01869898851404</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.86098291831775</v>
       </c>
       <c r="E84">
-        <v>-11.14163762995337</v>
+        <v>-12.09369041990397</v>
       </c>
       <c r="F84">
-        <v>1.041815744000822</v>
+        <v>0.04803473909186451</v>
       </c>
       <c r="G84">
-        <v>-2.579386223227165</v>
+        <v>-1.643647284370007</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.68300301268799</v>
       </c>
       <c r="E85">
-        <v>-13.42782867577774</v>
+        <v>-12.18242133961026</v>
       </c>
       <c r="F85">
-        <v>0.9925941641489637</v>
+        <v>-0.3238138668826137</v>
       </c>
       <c r="G85">
-        <v>-2.602477278363581</v>
+        <v>-1.590652071377354</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.52728650769446</v>
       </c>
       <c r="E86">
-        <v>-14.43407371417812</v>
+        <v>-14.42935051578812</v>
       </c>
       <c r="F86">
-        <v>0.8254561766571462</v>
+        <v>-0.1963785948379054</v>
       </c>
       <c r="G86">
-        <v>-2.053390195220063</v>
+        <v>-0.3676736488053312</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.39107635744324</v>
       </c>
       <c r="E87">
-        <v>-15.7980908415545</v>
+        <v>-15.62235887921285</v>
       </c>
       <c r="F87">
-        <v>0.6967753199099448</v>
+        <v>-0.158349064690458</v>
       </c>
       <c r="G87">
-        <v>-0.9655879681075611</v>
+        <v>-1.898496390528642</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.27232738949446</v>
       </c>
       <c r="E88">
-        <v>-15.79622963873735</v>
+        <v>-16.13848717576307</v>
       </c>
       <c r="F88">
-        <v>0.6925088161737509</v>
+        <v>-0.1782879221658406</v>
       </c>
       <c r="G88">
-        <v>-1.69577844497691</v>
+        <v>-0.7944724902737119</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.18561373868535</v>
       </c>
       <c r="E89">
-        <v>-18.6609921092037</v>
+        <v>-18.41188981098977</v>
       </c>
       <c r="F89">
-        <v>0.5307934377363981</v>
+        <v>-0.4714730634674837</v>
       </c>
       <c r="G89">
-        <v>-1.214779351939582</v>
+        <v>-1.400179833775386</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-14.13743507065051</v>
       </c>
       <c r="E90">
-        <v>-19.87865801360019</v>
+        <v>-20.22069365539954</v>
       </c>
       <c r="F90">
-        <v>0.2169844861509448</v>
+        <v>-0.5193754162917807</v>
       </c>
       <c r="G90">
-        <v>-1.286803580691966</v>
+        <v>-0.4547741019435562</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.12952220843735</v>
       </c>
       <c r="E91">
-        <v>-21.68968533874772</v>
+        <v>-21.70537197271029</v>
       </c>
       <c r="F91">
-        <v>-0.002312063812913245</v>
+        <v>-0.7382182345108653</v>
       </c>
       <c r="G91">
-        <v>-0.8151865737129318</v>
+        <v>-1.119975259331473</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-14.17808157963833</v>
       </c>
       <c r="E92">
-        <v>-23.18250585232427</v>
+        <v>-23.10609691039285</v>
       </c>
       <c r="F92">
-        <v>0.1631115620254411</v>
+        <v>-0.8093361323495891</v>
       </c>
       <c r="G92">
-        <v>-1.284406745721533</v>
+        <v>-0.1874442391018685</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.29015173351034</v>
       </c>
       <c r="E93">
-        <v>-26.53866662278496</v>
+        <v>-27.01258048463567</v>
       </c>
       <c r="F93">
-        <v>-0.374820283301172</v>
+        <v>-0.8944143978329117</v>
       </c>
       <c r="G93">
-        <v>-0.6434387816810818</v>
+        <v>-0.1853850797764418</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.45865829043695</v>
       </c>
       <c r="E94">
-        <v>-27.68696083385795</v>
+        <v>-29.39334871011024</v>
       </c>
       <c r="F94">
-        <v>-0.4075831994268256</v>
+        <v>-0.6422171493287568</v>
       </c>
       <c r="G94">
-        <v>-1.000653266459521</v>
+        <v>-1.13552489172943</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.68633004701943</v>
       </c>
       <c r="E95">
-        <v>-30.00866417285046</v>
+        <v>-30.12879779556294</v>
       </c>
       <c r="F95">
-        <v>-0.6320117484096651</v>
+        <v>-0.7566866210437624</v>
       </c>
       <c r="G95">
-        <v>-1.837943202069833</v>
+        <v>-0.5742053428183035</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.966151784268</v>
       </c>
       <c r="E96">
-        <v>-32.2523305835058</v>
+        <v>-33.05097452373555</v>
       </c>
       <c r="F96">
-        <v>-0.8165546639121621</v>
+        <v>-0.8963362249612975</v>
       </c>
       <c r="G96">
-        <v>-1.643064628355095</v>
+        <v>-0.5104972044605688</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.27440986678504</v>
       </c>
       <c r="E97">
-        <v>-34.64251577067931</v>
+        <v>-35.40885131310133</v>
       </c>
       <c r="F97">
-        <v>-0.9385087297835345</v>
+        <v>-1.090986351616129</v>
       </c>
       <c r="G97">
-        <v>-1.92707964071471</v>
+        <v>-1.214047721375403</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.59467481898735</v>
       </c>
       <c r="E98">
-        <v>-38.91029005820209</v>
+        <v>-38.12333637362314</v>
       </c>
       <c r="F98">
-        <v>-1.104090726213433</v>
+        <v>-1.109495914502828</v>
       </c>
       <c r="G98">
-        <v>-1.379968953258136</v>
+        <v>-1.995280189369235</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.90749879984106</v>
       </c>
       <c r="E99">
-        <v>-40.63234192604691</v>
+        <v>-41.41926843978181</v>
       </c>
       <c r="F99">
-        <v>-1.282155492668825</v>
+        <v>-1.20915219293777</v>
       </c>
       <c r="G99">
-        <v>-1.980879316273406</v>
+        <v>-1.740540331213396</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.19526561329738</v>
       </c>
       <c r="E100">
-        <v>-44.27455507838712</v>
+        <v>-43.04206068585251</v>
       </c>
       <c r="F100">
-        <v>-1.422132923710856</v>
+        <v>-1.490016102217295</v>
       </c>
       <c r="G100">
-        <v>-2.003493652852167</v>
+        <v>-2.411366105472534</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.42634730214121</v>
       </c>
       <c r="E101">
-        <v>-46.08173999333913</v>
+        <v>-46.93141304292432</v>
       </c>
       <c r="F101">
-        <v>-1.675905167747915</v>
+        <v>-1.267007345587646</v>
       </c>
       <c r="G101">
-        <v>-2.911861001190631</v>
+        <v>-2.329363892464787</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.61151666040395</v>
       </c>
       <c r="E102">
-        <v>-48.49280937051752</v>
+        <v>-48.64495704022723</v>
       </c>
       <c r="F102">
-        <v>-1.697622526966336</v>
+        <v>-1.614563486525199</v>
       </c>
       <c r="G102">
-        <v>-2.555285451701271</v>
+        <v>-1.835235175818709</v>
       </c>
     </row>
   </sheetData>
